--- a/excel_lotto_records/lotto.xlsx
+++ b/excel_lotto_records/lotto.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,41 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3771"/>
+  <dimension ref="A1:G3775"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Unnamed: 0</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Numbers</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>PB</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>PPX</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Winners WV Only</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Payout WV Only</t>
         </is>
@@ -103234,6 +103222,90 @@
       <c r="E3771" t="inlineStr"/>
       <c r="F3771" t="inlineStr"/>
       <c r="G3771" t="inlineStr"/>
+    </row>
+    <row r="3772">
+      <c r="A3772" t="n">
+        <v>3770</v>
+      </c>
+      <c r="B3772" t="inlineStr">
+        <is>
+          <t>10/12/2026</t>
+        </is>
+      </c>
+      <c r="C3772" t="inlineStr">
+        <is>
+          <t>22-28-38-51-69</t>
+        </is>
+      </c>
+      <c r="D3772" t="n">
+        <v>9</v>
+      </c>
+      <c r="E3772" t="inlineStr"/>
+      <c r="F3772" t="inlineStr"/>
+      <c r="G3772" t="inlineStr"/>
+    </row>
+    <row r="3773">
+      <c r="A3773" t="n">
+        <v>3771</v>
+      </c>
+      <c r="B3773" t="inlineStr">
+        <is>
+          <t>10/14/2026</t>
+        </is>
+      </c>
+      <c r="C3773" t="inlineStr">
+        <is>
+          <t>3-34-37-42-46</t>
+        </is>
+      </c>
+      <c r="D3773" t="n">
+        <v>20</v>
+      </c>
+      <c r="E3773" t="inlineStr"/>
+      <c r="F3773" t="inlineStr"/>
+      <c r="G3773" t="inlineStr"/>
+    </row>
+    <row r="3774">
+      <c r="A3774" t="n">
+        <v>3772</v>
+      </c>
+      <c r="B3774" t="inlineStr">
+        <is>
+          <t>10/17/2026</t>
+        </is>
+      </c>
+      <c r="C3774" t="inlineStr">
+        <is>
+          <t>12-13-24-32-35</t>
+        </is>
+      </c>
+      <c r="D3774" t="n">
+        <v>11</v>
+      </c>
+      <c r="E3774" t="inlineStr"/>
+      <c r="F3774" t="inlineStr"/>
+      <c r="G3774" t="inlineStr"/>
+    </row>
+    <row r="3775">
+      <c r="A3775" t="n">
+        <v>3773</v>
+      </c>
+      <c r="B3775" t="inlineStr">
+        <is>
+          <t>10/19/2026</t>
+        </is>
+      </c>
+      <c r="C3775" t="inlineStr">
+        <is>
+          <t>8-31-32-42-48</t>
+        </is>
+      </c>
+      <c r="D3775" t="n">
+        <v>23</v>
+      </c>
+      <c r="E3775" t="inlineStr"/>
+      <c r="F3775" t="inlineStr"/>
+      <c r="G3775" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
